--- a/coronavirus_response_forms/007_recently_contacted_list--coronavirus_response_forms.xlsx
+++ b/coronavirus_response_forms/007_recently_contacted_list--coronavirus_response_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +432,7 @@
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -865,7 +865,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Doctor Phone</t>
+          <t>Doctor Email</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -906,12 +906,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>doctor_phone</t>
+          <t>doctor_phone_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Doctor</t>
+          <t>Doctor Phone 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -929,12 +929,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>doctor_email</t>
+          <t>doctor_email_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Doctor</t>
+          <t>Doctor Email 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -957,7 +957,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Doctor</t>
+          <t>Doctor Relationship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -980,7 +980,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Doctor</t>
+          <t>Doctor Note</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Doctor</t>
+          <t>Doctor Relationship 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Patient</t>
+          <t>Patient Phone</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Patient</t>
+          <t>Patient Email</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
